--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796212</v>
+        <v>119795089</v>
       </c>
       <c r="B3" t="n">
-        <v>95455</v>
+        <v>90582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514064</v>
+        <v>514287</v>
       </c>
       <c r="R3" t="n">
-        <v>6791315</v>
+        <v>6791297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119795089</v>
+        <v>119800022</v>
       </c>
       <c r="B4" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514287</v>
+        <v>514109</v>
       </c>
       <c r="R4" t="n">
-        <v>6791297</v>
+        <v>6790972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119799502</v>
+        <v>119796212</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,47 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514168</v>
+        <v>514064</v>
       </c>
       <c r="R5" t="n">
-        <v>6790929</v>
+        <v>6791315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1080,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119799949</v>
+        <v>119799502</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1136,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1150,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514186</v>
+        <v>514168</v>
       </c>
       <c r="R6" t="n">
-        <v>6790923</v>
+        <v>6790929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119800022</v>
+        <v>119799949</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,38 +1215,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514109</v>
+        <v>514186</v>
       </c>
       <c r="R7" t="n">
-        <v>6790972</v>
+        <v>6790923</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,12 +1302,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119795197</v>
+        <v>119799989</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,38 +1983,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514150</v>
+        <v>514153</v>
       </c>
       <c r="R14" t="n">
-        <v>6791307</v>
+        <v>6790868</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119799651</v>
+        <v>119795197</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2106,26 +2106,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514163</v>
+        <v>514150</v>
       </c>
       <c r="R15" t="n">
-        <v>6790947</v>
+        <v>6791307</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119799465</v>
+        <v>119799651</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2219,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2233,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514129</v>
+        <v>514163</v>
       </c>
       <c r="R16" t="n">
-        <v>6790844</v>
+        <v>6790947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,19 +2274,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119795251</v>
+        <v>119799465</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2330,7 +2321,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2340,14 +2331,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514156</v>
+        <v>514129</v>
       </c>
       <c r="R17" t="n">
-        <v>6791319</v>
+        <v>6790844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,19 +2385,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119799413</v>
+        <v>119795251</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2441,7 +2432,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2451,14 +2442,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514145</v>
+        <v>514156</v>
       </c>
       <c r="R18" t="n">
-        <v>6790919</v>
+        <v>6791319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799989</v>
+        <v>119799413</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,38 +2520,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514153</v>
+        <v>514145</v>
       </c>
       <c r="R19" t="n">
-        <v>6790868</v>
+        <v>6790919</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119790568</v>
+        <v>119796962</v>
       </c>
       <c r="B20" t="n">
-        <v>95202</v>
+        <v>79511</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514543</v>
+        <v>514045</v>
       </c>
       <c r="R20" t="n">
-        <v>6790975</v>
+        <v>6791074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,19 +2709,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119794869</v>
+        <v>119790568</v>
       </c>
       <c r="B21" t="n">
         <v>95202</v>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514269</v>
+        <v>514543</v>
       </c>
       <c r="R21" t="n">
-        <v>6791300</v>
+        <v>6790975</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119796962</v>
+        <v>119794869</v>
       </c>
       <c r="B22" t="n">
-        <v>79511</v>
+        <v>95202</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514045</v>
+        <v>514269</v>
       </c>
       <c r="R22" t="n">
-        <v>6791074</v>
+        <v>6791300</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119795064</v>
+        <v>119800323</v>
       </c>
       <c r="B30" t="n">
-        <v>95202</v>
+        <v>82305</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3669,25 +3669,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514226</v>
+        <v>514384</v>
       </c>
       <c r="R30" t="n">
-        <v>6791259</v>
+        <v>6790930</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119798721</v>
+        <v>119795064</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,47 +3771,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513988</v>
+        <v>514226</v>
       </c>
       <c r="R31" t="n">
-        <v>6790833</v>
+        <v>6791259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,10 +3861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119800323</v>
+        <v>119798721</v>
       </c>
       <c r="B32" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3882,38 +3873,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514384</v>
+        <v>513988</v>
       </c>
       <c r="R32" t="n">
-        <v>6790930</v>
+        <v>6790833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -3138,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119790576</v>
+        <v>119793661</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,47 +3150,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514526</v>
+        <v>514334</v>
       </c>
       <c r="R25" t="n">
-        <v>6790968</v>
+        <v>6791247</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,22 +3228,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119793661</v>
+        <v>119790576</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,38 +3252,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514334</v>
+        <v>514526</v>
       </c>
       <c r="R26" t="n">
-        <v>6791247</v>
+        <v>6790968</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,12 +3339,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119799930</v>
+        <v>119798721</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514109</v>
+        <v>513988</v>
       </c>
       <c r="R2" t="n">
-        <v>6790972</v>
+        <v>6790833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119795089</v>
+        <v>119799962</v>
       </c>
       <c r="B3" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514287</v>
+        <v>514169</v>
       </c>
       <c r="R3" t="n">
-        <v>6791297</v>
+        <v>6790900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119800022</v>
+        <v>119799787</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +909,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514109</v>
+        <v>514108</v>
       </c>
       <c r="R4" t="n">
-        <v>6790972</v>
+        <v>6790973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796212</v>
+        <v>119790169</v>
       </c>
       <c r="B5" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1020,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514064</v>
+        <v>514594</v>
       </c>
       <c r="R5" t="n">
-        <v>6791315</v>
+        <v>6790980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,19 +1107,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119799502</v>
+        <v>119795232</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1127,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1137,14 +1164,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514168</v>
+        <v>514150</v>
       </c>
       <c r="R6" t="n">
-        <v>6790929</v>
+        <v>6791303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119799949</v>
+        <v>119799413</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1238,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514186</v>
+        <v>514145</v>
       </c>
       <c r="R7" t="n">
-        <v>6790923</v>
+        <v>6790919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119791871</v>
+        <v>119800022</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,47 +1353,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514417</v>
+        <v>514109</v>
       </c>
       <c r="R8" t="n">
-        <v>6790984</v>
+        <v>6790972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,22 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796795</v>
+        <v>119796962</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,47 +1455,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514065</v>
+        <v>514045</v>
       </c>
       <c r="R9" t="n">
-        <v>6791124</v>
+        <v>6791074</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,19 +1533,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119797621</v>
+        <v>119797154</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1638,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119799570</v>
+        <v>119796212</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,47 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514165</v>
+        <v>514064</v>
       </c>
       <c r="R11" t="n">
-        <v>6790935</v>
+        <v>6791315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,19 +1737,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119799865</v>
+        <v>119799688</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514173</v>
+        <v>514139</v>
       </c>
       <c r="R12" t="n">
-        <v>6790969</v>
+        <v>6790955</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119799962</v>
+        <v>119791577</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514169</v>
+        <v>514442</v>
       </c>
       <c r="R13" t="n">
-        <v>6790900</v>
+        <v>6790946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119799989</v>
+        <v>119794869</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>95202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514153</v>
+        <v>514269</v>
       </c>
       <c r="R14" t="n">
-        <v>6790868</v>
+        <v>6791300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119795197</v>
+        <v>119800029</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,38 +2085,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514150</v>
+        <v>514147</v>
       </c>
       <c r="R15" t="n">
-        <v>6791307</v>
+        <v>6790803</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119799651</v>
+        <v>119799570</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514163</v>
+        <v>514165</v>
       </c>
       <c r="R16" t="n">
-        <v>6790947</v>
+        <v>6790935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119799465</v>
+        <v>119796795</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514129</v>
+        <v>514065</v>
       </c>
       <c r="R17" t="n">
-        <v>6790844</v>
+        <v>6791124</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,19 +2385,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119795251</v>
+        <v>119796166</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514156</v>
+        <v>514100</v>
       </c>
       <c r="R18" t="n">
-        <v>6791319</v>
+        <v>6791324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799413</v>
+        <v>119799502</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514145</v>
+        <v>514168</v>
       </c>
       <c r="R19" t="n">
-        <v>6790919</v>
+        <v>6790929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796962</v>
+        <v>119799465</v>
       </c>
       <c r="B20" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,38 +2631,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514045</v>
+        <v>514129</v>
       </c>
       <c r="R20" t="n">
-        <v>6791074</v>
+        <v>6790844</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119790568</v>
+        <v>119790391</v>
       </c>
       <c r="B21" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,38 +2742,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514543</v>
+        <v>514546</v>
       </c>
       <c r="R21" t="n">
-        <v>6790975</v>
+        <v>6790985</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,22 +2829,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119794869</v>
+        <v>119795263</v>
       </c>
       <c r="B22" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,38 +2853,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514269</v>
+        <v>514162</v>
       </c>
       <c r="R22" t="n">
-        <v>6791300</v>
+        <v>6791322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119799531</v>
+        <v>119794575</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2965,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514129</v>
+        <v>514311</v>
       </c>
       <c r="R23" t="n">
-        <v>6790844</v>
+        <v>6791261</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119795263</v>
+        <v>119793661</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,47 +3066,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514162</v>
+        <v>514334</v>
       </c>
       <c r="R24" t="n">
-        <v>6791322</v>
+        <v>6791247</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,7 +3156,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119793661</v>
+        <v>119800000</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3178,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514334</v>
+        <v>514156</v>
       </c>
       <c r="R25" t="n">
-        <v>6791247</v>
+        <v>6790891</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119790576</v>
+        <v>119800271</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>97811</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3252,47 +3270,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514526</v>
+        <v>514404</v>
       </c>
       <c r="R26" t="n">
-        <v>6790968</v>
+        <v>6790910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,22 +3348,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119794575</v>
+        <v>119790576</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,38 +3372,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514311</v>
+        <v>514526</v>
       </c>
       <c r="R27" t="n">
-        <v>6791261</v>
+        <v>6790968</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3453,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119795093</v>
+        <v>119799988</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,38 +3483,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514237</v>
+        <v>514109</v>
       </c>
       <c r="R28" t="n">
-        <v>6791250</v>
+        <v>6790972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,22 +3570,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119800000</v>
+        <v>119791871</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3567,38 +3594,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514156</v>
+        <v>514417</v>
       </c>
       <c r="R29" t="n">
-        <v>6790891</v>
+        <v>6790984</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,10 +3693,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119800323</v>
+        <v>119795251</v>
       </c>
       <c r="B30" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3669,38 +3705,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514384</v>
+        <v>514156</v>
       </c>
       <c r="R30" t="n">
-        <v>6790930</v>
+        <v>6791319</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3804,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119795064</v>
+        <v>119795197</v>
       </c>
       <c r="B31" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,38 +3816,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514226</v>
+        <v>514150</v>
       </c>
       <c r="R31" t="n">
-        <v>6791259</v>
+        <v>6791307</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,10 +3906,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119798721</v>
+        <v>119790568</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,47 +3918,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513988</v>
+        <v>514543</v>
       </c>
       <c r="R32" t="n">
-        <v>6790833</v>
+        <v>6790975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,10 +4008,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119800029</v>
+        <v>119795133</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>90546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3984,25 +4020,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514147</v>
+        <v>514253</v>
       </c>
       <c r="R33" t="n">
-        <v>6790803</v>
+        <v>6791221</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,6 +4094,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4074,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119800271</v>
+        <v>119794317</v>
       </c>
       <c r="B34" t="n">
-        <v>97811</v>
+        <v>78782</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,21 +4146,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220093</v>
+        <v>6459</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514404</v>
+        <v>514338</v>
       </c>
       <c r="R34" t="n">
-        <v>6790910</v>
+        <v>6791271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4160,6 +4216,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4287,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119790391</v>
+        <v>119799949</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4322,7 +4398,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4336,10 +4412,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514546</v>
+        <v>514186</v>
       </c>
       <c r="R36" t="n">
-        <v>6790985</v>
+        <v>6790923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4386,22 +4462,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119796166</v>
+        <v>119795089</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4410,47 +4486,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514100</v>
+        <v>514287</v>
       </c>
       <c r="R37" t="n">
-        <v>6791324</v>
+        <v>6791297</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,22 +4564,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119794317</v>
+        <v>119799531</v>
       </c>
       <c r="B38" t="n">
-        <v>78782</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4521,25 +4588,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4549,10 +4616,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514338</v>
+        <v>514129</v>
       </c>
       <c r="R38" t="n">
-        <v>6791271</v>
+        <v>6790844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4596,45 +4663,25 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119791577</v>
+        <v>119800323</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,47 +4690,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514442</v>
+        <v>514384</v>
       </c>
       <c r="R39" t="n">
-        <v>6790946</v>
+        <v>6790930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4742,7 +4780,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119799906</v>
+        <v>119799865</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -4777,7 +4815,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4791,10 +4829,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514171</v>
+        <v>514173</v>
       </c>
       <c r="R40" t="n">
-        <v>6790973</v>
+        <v>6790969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4853,10 +4891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119800164</v>
+        <v>119799651</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4865,38 +4903,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514290</v>
+        <v>514163</v>
       </c>
       <c r="R41" t="n">
-        <v>6790882</v>
+        <v>6790947</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4955,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119790198</v>
+        <v>119800164</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4967,47 +5014,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514585</v>
+        <v>514290</v>
       </c>
       <c r="R42" t="n">
-        <v>6790974</v>
+        <v>6790882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5104,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119795232</v>
+        <v>119799989</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5078,47 +5116,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514150</v>
+        <v>514153</v>
       </c>
       <c r="R43" t="n">
-        <v>6791303</v>
+        <v>6790868</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5177,10 +5206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119799787</v>
+        <v>119795064</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5189,47 +5218,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514108</v>
+        <v>514226</v>
       </c>
       <c r="R44" t="n">
-        <v>6790973</v>
+        <v>6791259</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5276,22 +5296,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119790169</v>
+        <v>119799434</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5300,47 +5320,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514594</v>
+        <v>514151</v>
       </c>
       <c r="R45" t="n">
-        <v>6790980</v>
+        <v>6790903</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,10 +5410,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119795035</v>
+        <v>119795093</v>
       </c>
       <c r="B46" t="n">
-        <v>91861</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5411,25 +5422,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5439,10 +5450,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514287</v>
+        <v>514237</v>
       </c>
       <c r="R46" t="n">
-        <v>6791297</v>
+        <v>6791250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5489,22 +5500,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119795133</v>
+        <v>119799906</v>
       </c>
       <c r="B47" t="n">
-        <v>90546</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5513,38 +5524,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514253</v>
+        <v>514171</v>
       </c>
       <c r="R47" t="n">
-        <v>6791221</v>
+        <v>6790973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,26 +5607,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5623,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119795157</v>
+        <v>119790198</v>
       </c>
       <c r="B48" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,38 +5635,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514196</v>
+        <v>514585</v>
       </c>
       <c r="R48" t="n">
-        <v>6791241</v>
+        <v>6790974</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119799434</v>
+        <v>119795157</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5737,25 +5746,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5765,10 +5774,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514151</v>
+        <v>514196</v>
       </c>
       <c r="R49" t="n">
-        <v>6790903</v>
+        <v>6791241</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5827,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119799688</v>
+        <v>119795035</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5839,47 +5848,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514139</v>
+        <v>514287</v>
       </c>
       <c r="R50" t="n">
-        <v>6790955</v>
+        <v>6791297</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119798721</v>
+        <v>119799787</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513988</v>
+        <v>514108</v>
       </c>
       <c r="R2" t="n">
-        <v>6790833</v>
+        <v>6790973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119799962</v>
+        <v>119790169</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514169</v>
+        <v>514594</v>
       </c>
       <c r="R3" t="n">
-        <v>6790900</v>
+        <v>6790980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119799787</v>
+        <v>119795232</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -942,14 +942,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514108</v>
+        <v>514150</v>
       </c>
       <c r="R4" t="n">
-        <v>6790973</v>
+        <v>6791303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +996,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119790169</v>
+        <v>119798721</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514594</v>
+        <v>513988</v>
       </c>
       <c r="R5" t="n">
-        <v>6790980</v>
+        <v>6790833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119795232</v>
+        <v>119799962</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,14 +1164,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514150</v>
+        <v>514169</v>
       </c>
       <c r="R6" t="n">
-        <v>6791303</v>
+        <v>6790900</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799502</v>
+        <v>119799465</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514168</v>
+        <v>514129</v>
       </c>
       <c r="R19" t="n">
-        <v>6790929</v>
+        <v>6790844</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,19 +2607,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119799465</v>
+        <v>119790391</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514129</v>
+        <v>514546</v>
       </c>
       <c r="R20" t="n">
-        <v>6790844</v>
+        <v>6790985</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119790391</v>
+        <v>119799502</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514546</v>
+        <v>514168</v>
       </c>
       <c r="R21" t="n">
-        <v>6790985</v>
+        <v>6790929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,12 +2829,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119799787</v>
+        <v>119795093</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514108</v>
+        <v>514237</v>
       </c>
       <c r="R2" t="n">
-        <v>6790973</v>
+        <v>6791250</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119790169</v>
+        <v>119790568</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514594</v>
+        <v>514543</v>
       </c>
       <c r="R3" t="n">
-        <v>6790980</v>
+        <v>6790975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119795232</v>
+        <v>119800164</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514150</v>
+        <v>514290</v>
       </c>
       <c r="R4" t="n">
-        <v>6791303</v>
+        <v>6790882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119798721</v>
+        <v>119796962</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513988</v>
+        <v>514045</v>
       </c>
       <c r="R5" t="n">
-        <v>6790833</v>
+        <v>6791074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119799962</v>
+        <v>119795263</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1154,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,14 +1128,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514169</v>
+        <v>514162</v>
       </c>
       <c r="R6" t="n">
-        <v>6790900</v>
+        <v>6791322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119799413</v>
+        <v>119796795</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1265,7 +1229,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1279,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514145</v>
+        <v>514065</v>
       </c>
       <c r="R7" t="n">
-        <v>6790919</v>
+        <v>6791124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119800022</v>
+        <v>119799502</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,38 +1317,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514109</v>
+        <v>514168</v>
       </c>
       <c r="R8" t="n">
-        <v>6790972</v>
+        <v>6790929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,22 +1404,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796962</v>
+        <v>119790576</v>
       </c>
       <c r="B9" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,38 +1428,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514045</v>
+        <v>514526</v>
       </c>
       <c r="R9" t="n">
-        <v>6791074</v>
+        <v>6790968</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119797154</v>
+        <v>119799688</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,38 +1539,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514045</v>
+        <v>514139</v>
       </c>
       <c r="R10" t="n">
-        <v>6791074</v>
+        <v>6790955</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796212</v>
+        <v>119795157</v>
       </c>
       <c r="B11" t="n">
-        <v>95455</v>
+        <v>95202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1650,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514064</v>
+        <v>514196</v>
       </c>
       <c r="R11" t="n">
-        <v>6791315</v>
+        <v>6791241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,22 +1728,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119799688</v>
+        <v>119800000</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,47 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514139</v>
+        <v>514156</v>
       </c>
       <c r="R12" t="n">
-        <v>6790955</v>
+        <v>6790891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119791577</v>
+        <v>119790365</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1895,7 +1877,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1909,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514442</v>
+        <v>514567</v>
       </c>
       <c r="R13" t="n">
-        <v>6790946</v>
+        <v>6790978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119794869</v>
+        <v>119799465</v>
       </c>
       <c r="B14" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,38 +1965,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514269</v>
+        <v>514129</v>
       </c>
       <c r="R14" t="n">
-        <v>6791300</v>
+        <v>6790844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,22 +2052,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119800029</v>
+        <v>119799906</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,38 +2076,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514147</v>
+        <v>514171</v>
       </c>
       <c r="R15" t="n">
-        <v>6790803</v>
+        <v>6790973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119799570</v>
+        <v>119799413</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514165</v>
+        <v>514145</v>
       </c>
       <c r="R16" t="n">
-        <v>6790935</v>
+        <v>6790919</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796795</v>
+        <v>119791871</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514065</v>
+        <v>514417</v>
       </c>
       <c r="R17" t="n">
-        <v>6791124</v>
+        <v>6790984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796166</v>
+        <v>119799570</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2442,14 +2442,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514100</v>
+        <v>514165</v>
       </c>
       <c r="R18" t="n">
-        <v>6791324</v>
+        <v>6790935</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799465</v>
+        <v>119799434</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,47 +2520,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514129</v>
+        <v>514151</v>
       </c>
       <c r="R19" t="n">
-        <v>6790844</v>
+        <v>6790903</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,22 +2598,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119790391</v>
+        <v>119795035</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,47 +2622,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514546</v>
+        <v>514287</v>
       </c>
       <c r="R20" t="n">
-        <v>6790985</v>
+        <v>6791297</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,7 +2712,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119799502</v>
+        <v>119799949</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2765,7 +2747,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2779,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514168</v>
+        <v>514186</v>
       </c>
       <c r="R21" t="n">
-        <v>6790929</v>
+        <v>6790923</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2841,7 +2823,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119795263</v>
+        <v>119790198</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2876,7 +2858,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2886,14 +2868,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514162</v>
+        <v>514585</v>
       </c>
       <c r="R22" t="n">
-        <v>6791322</v>
+        <v>6790974</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119794575</v>
+        <v>119800029</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,21 +2950,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514311</v>
+        <v>514147</v>
       </c>
       <c r="R23" t="n">
-        <v>6791261</v>
+        <v>6790803</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,22 +3024,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119793661</v>
+        <v>119795197</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,38 +3048,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514334</v>
+        <v>514150</v>
       </c>
       <c r="R24" t="n">
-        <v>6791247</v>
+        <v>6791307</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119800000</v>
+        <v>119799930</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3168,38 +3150,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514156</v>
+        <v>514109</v>
       </c>
       <c r="R25" t="n">
-        <v>6790891</v>
+        <v>6790972</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,22 +3237,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119800271</v>
+        <v>119799865</v>
       </c>
       <c r="B26" t="n">
-        <v>97811</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,38 +3261,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514404</v>
+        <v>514173</v>
       </c>
       <c r="R26" t="n">
-        <v>6790910</v>
+        <v>6790969</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119790576</v>
+        <v>119797621</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,47 +3372,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514526</v>
+        <v>514045</v>
       </c>
       <c r="R27" t="n">
-        <v>6790968</v>
+        <v>6791074</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119799988</v>
+        <v>119794575</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,47 +3474,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514109</v>
+        <v>514311</v>
       </c>
       <c r="R28" t="n">
-        <v>6790972</v>
+        <v>6791261</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3582,7 +3564,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119791871</v>
+        <v>119791577</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3617,7 +3599,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3631,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514417</v>
+        <v>514442</v>
       </c>
       <c r="R29" t="n">
-        <v>6790984</v>
+        <v>6790946</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3804,7 +3786,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119795197</v>
+        <v>119799651</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3837,17 +3819,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514150</v>
+        <v>514163</v>
       </c>
       <c r="R31" t="n">
-        <v>6791307</v>
+        <v>6790947</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3906,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119790568</v>
+        <v>119799787</v>
       </c>
       <c r="B32" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,38 +3909,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514543</v>
+        <v>514108</v>
       </c>
       <c r="R32" t="n">
-        <v>6790975</v>
+        <v>6790973</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,22 +3996,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119795133</v>
+        <v>119790391</v>
       </c>
       <c r="B33" t="n">
-        <v>90546</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4020,38 +4020,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514253</v>
+        <v>514546</v>
       </c>
       <c r="R33" t="n">
-        <v>6791221</v>
+        <v>6790985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4095,45 +4104,25 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119794317</v>
+        <v>119796212</v>
       </c>
       <c r="B34" t="n">
-        <v>78782</v>
+        <v>95455</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,38 +4131,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6459</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514338</v>
+        <v>514064</v>
       </c>
       <c r="R34" t="n">
-        <v>6791271</v>
+        <v>6791315</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,42 +4206,22 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119790365</v>
+        <v>119799962</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4287,7 +4256,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4301,10 +4270,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514567</v>
+        <v>514169</v>
       </c>
       <c r="R35" t="n">
-        <v>6790978</v>
+        <v>6790900</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,7 +4332,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119799949</v>
+        <v>119798721</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4398,7 +4367,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4412,10 +4381,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514186</v>
+        <v>513988</v>
       </c>
       <c r="R36" t="n">
-        <v>6790923</v>
+        <v>6790833</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4474,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119795089</v>
+        <v>119793661</v>
       </c>
       <c r="B37" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4490,21 +4459,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4514,10 +4483,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514287</v>
+        <v>514334</v>
       </c>
       <c r="R37" t="n">
-        <v>6791297</v>
+        <v>6791247</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4564,19 +4533,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119799531</v>
+        <v>119800022</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4616,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514129</v>
+        <v>514109</v>
       </c>
       <c r="R38" t="n">
-        <v>6790844</v>
+        <v>6790972</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4678,10 +4647,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119800323</v>
+        <v>119794869</v>
       </c>
       <c r="B39" t="n">
-        <v>82305</v>
+        <v>95202</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4690,25 +4659,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4718,10 +4687,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514384</v>
+        <v>514269</v>
       </c>
       <c r="R39" t="n">
-        <v>6790930</v>
+        <v>6791300</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4780,10 +4749,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119799865</v>
+        <v>119794317</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>78782</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4792,47 +4761,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6459</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514173</v>
+        <v>514338</v>
       </c>
       <c r="R40" t="n">
-        <v>6790969</v>
+        <v>6791271</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,6 +4835,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4891,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119799651</v>
+        <v>119795089</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4903,47 +4883,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514163</v>
+        <v>514287</v>
       </c>
       <c r="R41" t="n">
-        <v>6790947</v>
+        <v>6791297</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,22 +4961,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119800164</v>
+        <v>119800323</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5018,21 +4989,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5042,10 +5013,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514290</v>
+        <v>514384</v>
       </c>
       <c r="R42" t="n">
-        <v>6790882</v>
+        <v>6790930</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5104,10 +5075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119799989</v>
+        <v>119795232</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5116,38 +5087,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514153</v>
+        <v>514150</v>
       </c>
       <c r="R43" t="n">
-        <v>6790868</v>
+        <v>6791303</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,10 +5186,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119795064</v>
+        <v>119796166</v>
       </c>
       <c r="B44" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5218,38 +5198,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514226</v>
+        <v>514100</v>
       </c>
       <c r="R44" t="n">
-        <v>6791259</v>
+        <v>6791324</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5308,10 +5297,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119799434</v>
+        <v>119790169</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5320,38 +5309,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514151</v>
+        <v>514594</v>
       </c>
       <c r="R45" t="n">
-        <v>6790903</v>
+        <v>6790980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5410,10 +5408,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119795093</v>
+        <v>119795064</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5422,25 +5420,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5450,10 +5448,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514237</v>
+        <v>514226</v>
       </c>
       <c r="R46" t="n">
-        <v>6791250</v>
+        <v>6791259</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5512,10 +5510,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119799906</v>
+        <v>119795133</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>90546</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5524,47 +5522,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514171</v>
+        <v>514253</v>
       </c>
       <c r="R47" t="n">
-        <v>6790973</v>
+        <v>6791221</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5607,6 +5596,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5623,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119790198</v>
+        <v>119800271</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>97811</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,47 +5644,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514585</v>
+        <v>514404</v>
       </c>
       <c r="R48" t="n">
-        <v>6790974</v>
+        <v>6790910</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119795157</v>
+        <v>119799531</v>
       </c>
       <c r="B49" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5746,25 +5746,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514196</v>
+        <v>514129</v>
       </c>
       <c r="R49" t="n">
-        <v>6791241</v>
+        <v>6790844</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,22 +5824,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119795035</v>
+        <v>119799989</v>
       </c>
       <c r="B50" t="n">
-        <v>91861</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514287</v>
+        <v>514153</v>
       </c>
       <c r="R50" t="n">
-        <v>6791297</v>
+        <v>6790868</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119800000</v>
+        <v>119790365</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514156</v>
+        <v>514567</v>
       </c>
       <c r="R12" t="n">
-        <v>6790891</v>
+        <v>6790978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119790365</v>
+        <v>119799465</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1877,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1891,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514567</v>
+        <v>514129</v>
       </c>
       <c r="R13" t="n">
-        <v>6790978</v>
+        <v>6790844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,19 +1950,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119799465</v>
+        <v>119799906</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -1988,7 +1997,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2002,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514129</v>
+        <v>514171</v>
       </c>
       <c r="R14" t="n">
-        <v>6790844</v>
+        <v>6790973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,22 +2061,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119799906</v>
+        <v>119800000</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,47 +2085,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514171</v>
+        <v>514156</v>
       </c>
       <c r="R15" t="n">
-        <v>6790973</v>
+        <v>6790891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119795232</v>
+        <v>119795064</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5087,47 +5087,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514150</v>
+        <v>514226</v>
       </c>
       <c r="R43" t="n">
-        <v>6791303</v>
+        <v>6791259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5186,7 +5177,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119796166</v>
+        <v>119795232</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5221,7 +5212,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5235,10 +5226,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514100</v>
+        <v>514150</v>
       </c>
       <c r="R44" t="n">
-        <v>6791324</v>
+        <v>6791303</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5297,7 +5288,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119790169</v>
+        <v>119796166</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5332,7 +5323,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5342,14 +5333,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514594</v>
+        <v>514100</v>
       </c>
       <c r="R45" t="n">
-        <v>6790980</v>
+        <v>6791324</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119795064</v>
+        <v>119790169</v>
       </c>
       <c r="B46" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5420,38 +5411,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514226</v>
+        <v>514594</v>
       </c>
       <c r="R46" t="n">
-        <v>6791259</v>
+        <v>6790980</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119795093</v>
+        <v>119799413</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514237</v>
+        <v>514145</v>
       </c>
       <c r="R2" t="n">
-        <v>6791250</v>
+        <v>6790919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119790568</v>
+        <v>119791577</v>
       </c>
       <c r="B3" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514543</v>
+        <v>514442</v>
       </c>
       <c r="R3" t="n">
-        <v>6790975</v>
+        <v>6790946</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119800164</v>
+        <v>119795064</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514290</v>
+        <v>514226</v>
       </c>
       <c r="R4" t="n">
-        <v>6790882</v>
+        <v>6791259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796962</v>
+        <v>119790568</v>
       </c>
       <c r="B5" t="n">
-        <v>79511</v>
+        <v>95202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514045</v>
+        <v>514543</v>
       </c>
       <c r="R5" t="n">
-        <v>6791074</v>
+        <v>6790975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119795263</v>
+        <v>119795093</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,47 +1113,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514162</v>
+        <v>514237</v>
       </c>
       <c r="R6" t="n">
-        <v>6791322</v>
+        <v>6791250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796795</v>
+        <v>119790391</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1229,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1243,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514065</v>
+        <v>514546</v>
       </c>
       <c r="R7" t="n">
-        <v>6791124</v>
+        <v>6790985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,19 +1302,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119799502</v>
+        <v>119796795</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1340,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1354,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514168</v>
+        <v>514065</v>
       </c>
       <c r="R8" t="n">
-        <v>6790929</v>
+        <v>6791124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119790576</v>
+        <v>119795035</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,47 +1437,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514526</v>
+        <v>514287</v>
       </c>
       <c r="R9" t="n">
-        <v>6790968</v>
+        <v>6791297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119799688</v>
+        <v>119799787</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514139</v>
+        <v>514108</v>
       </c>
       <c r="R10" t="n">
-        <v>6790955</v>
+        <v>6790973</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119795157</v>
+        <v>119795197</v>
       </c>
       <c r="B11" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,38 +1650,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514196</v>
+        <v>514150</v>
       </c>
       <c r="R11" t="n">
-        <v>6791241</v>
+        <v>6791307</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119790365</v>
+        <v>119797154</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,47 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514567</v>
+        <v>514045</v>
       </c>
       <c r="R12" t="n">
-        <v>6790978</v>
+        <v>6791074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,22 +1830,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119799465</v>
+        <v>119799989</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,47 +1854,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514129</v>
+        <v>514153</v>
       </c>
       <c r="R13" t="n">
-        <v>6790844</v>
+        <v>6790868</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,22 +1932,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119799906</v>
+        <v>119800029</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,47 +1956,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514171</v>
+        <v>514147</v>
       </c>
       <c r="R14" t="n">
-        <v>6790973</v>
+        <v>6790803</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119800000</v>
+        <v>119794869</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2058,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514156</v>
+        <v>514269</v>
       </c>
       <c r="R15" t="n">
-        <v>6790891</v>
+        <v>6791300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119799413</v>
+        <v>119794575</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,47 +2160,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514145</v>
+        <v>514311</v>
       </c>
       <c r="R16" t="n">
-        <v>6790919</v>
+        <v>6791261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,19 +2238,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119791871</v>
+        <v>119798721</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2321,7 +2285,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2335,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514417</v>
+        <v>513988</v>
       </c>
       <c r="R17" t="n">
-        <v>6790984</v>
+        <v>6790833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119799570</v>
+        <v>119800271</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97811</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,47 +2373,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514165</v>
+        <v>514404</v>
       </c>
       <c r="R18" t="n">
-        <v>6790935</v>
+        <v>6790910</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799434</v>
+        <v>119790169</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,38 +2475,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514151</v>
+        <v>514594</v>
       </c>
       <c r="R19" t="n">
-        <v>6790903</v>
+        <v>6790980</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,10 +2574,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119795035</v>
+        <v>119796212</v>
       </c>
       <c r="B20" t="n">
-        <v>91861</v>
+        <v>95455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,38 +2586,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514287</v>
+        <v>514064</v>
       </c>
       <c r="R20" t="n">
-        <v>6791297</v>
+        <v>6791315</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2676,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119799949</v>
+        <v>119795263</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2747,7 +2711,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2757,14 +2721,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514186</v>
+        <v>514162</v>
       </c>
       <c r="R21" t="n">
-        <v>6790923</v>
+        <v>6791322</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2787,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119790198</v>
+        <v>119799930</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2858,7 +2822,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2872,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514585</v>
+        <v>514109</v>
       </c>
       <c r="R22" t="n">
-        <v>6790974</v>
+        <v>6790972</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,22 +2886,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119800029</v>
+        <v>119800000</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,21 +2914,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514147</v>
+        <v>514156</v>
       </c>
       <c r="R23" t="n">
-        <v>6790803</v>
+        <v>6790891</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119795197</v>
+        <v>119799531</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,38 +3012,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514150</v>
+        <v>514129</v>
       </c>
       <c r="R24" t="n">
-        <v>6791307</v>
+        <v>6790844</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,19 +3090,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119799930</v>
+        <v>119799570</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3173,7 +3137,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3187,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514109</v>
+        <v>514165</v>
       </c>
       <c r="R25" t="n">
-        <v>6790972</v>
+        <v>6790935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,22 +3201,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119799865</v>
+        <v>119800022</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,47 +3225,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514173</v>
+        <v>514109</v>
       </c>
       <c r="R26" t="n">
-        <v>6790969</v>
+        <v>6790972</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3348,22 +3303,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119797621</v>
+        <v>119800323</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3376,21 +3331,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514045</v>
+        <v>514384</v>
       </c>
       <c r="R27" t="n">
-        <v>6791074</v>
+        <v>6790930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,22 +3405,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119794575</v>
+        <v>119795133</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>90546</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3474,25 +3429,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3502,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514311</v>
+        <v>514253</v>
       </c>
       <c r="R28" t="n">
-        <v>6791261</v>
+        <v>6791221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,22 +3504,42 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119791577</v>
+        <v>119799865</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3599,7 +3574,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3613,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514442</v>
+        <v>514173</v>
       </c>
       <c r="R29" t="n">
-        <v>6790946</v>
+        <v>6790969</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,7 +3650,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119795251</v>
+        <v>119796166</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3710,7 +3685,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3724,10 +3699,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514156</v>
+        <v>514100</v>
       </c>
       <c r="R30" t="n">
-        <v>6791319</v>
+        <v>6791324</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3761,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119799651</v>
+        <v>119799688</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3821,7 +3796,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3835,10 +3810,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514163</v>
+        <v>514139</v>
       </c>
       <c r="R31" t="n">
-        <v>6790947</v>
+        <v>6790955</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119799787</v>
+        <v>119796962</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,47 +3884,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514108</v>
+        <v>514045</v>
       </c>
       <c r="R32" t="n">
-        <v>6790973</v>
+        <v>6791074</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,7 +3974,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119790391</v>
+        <v>119799651</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4043,7 +4009,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4057,10 +4023,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514546</v>
+        <v>514163</v>
       </c>
       <c r="R33" t="n">
-        <v>6790985</v>
+        <v>6790947</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4107,22 +4073,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119796212</v>
+        <v>119799962</v>
       </c>
       <c r="B34" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4131,38 +4097,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514064</v>
+        <v>514169</v>
       </c>
       <c r="R34" t="n">
-        <v>6791315</v>
+        <v>6790900</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4209,19 +4184,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119799962</v>
+        <v>119799465</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4270,10 +4245,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514169</v>
+        <v>514129</v>
       </c>
       <c r="R35" t="n">
-        <v>6790900</v>
+        <v>6790844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,19 +4295,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119798721</v>
+        <v>119790198</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4367,7 +4342,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4381,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513988</v>
+        <v>514585</v>
       </c>
       <c r="R36" t="n">
-        <v>6790833</v>
+        <v>6790974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4443,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119793661</v>
+        <v>119799949</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4455,38 +4430,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514334</v>
+        <v>514186</v>
       </c>
       <c r="R37" t="n">
-        <v>6791247</v>
+        <v>6790923</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4545,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119800022</v>
+        <v>119799906</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,38 +4541,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514109</v>
+        <v>514171</v>
       </c>
       <c r="R38" t="n">
-        <v>6790972</v>
+        <v>6790973</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4635,22 +4628,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119794869</v>
+        <v>119799434</v>
       </c>
       <c r="B39" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4659,25 +4652,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4687,10 +4680,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514269</v>
+        <v>514151</v>
       </c>
       <c r="R39" t="n">
-        <v>6791300</v>
+        <v>6790903</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4749,10 +4742,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119794317</v>
+        <v>119800164</v>
       </c>
       <c r="B40" t="n">
-        <v>78782</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4761,25 +4754,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4789,10 +4782,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514338</v>
+        <v>514290</v>
       </c>
       <c r="R40" t="n">
-        <v>6791271</v>
+        <v>6790882</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4835,26 +4828,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4871,10 +4844,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119795089</v>
+        <v>119795157</v>
       </c>
       <c r="B41" t="n">
-        <v>90582</v>
+        <v>95202</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4883,25 +4856,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4911,10 +4884,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514287</v>
+        <v>514196</v>
       </c>
       <c r="R41" t="n">
-        <v>6791297</v>
+        <v>6791241</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4961,22 +4934,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119800323</v>
+        <v>119795251</v>
       </c>
       <c r="B42" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4985,38 +4958,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514384</v>
+        <v>514156</v>
       </c>
       <c r="R42" t="n">
-        <v>6790930</v>
+        <v>6791319</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,10 +5057,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119795064</v>
+        <v>119795089</v>
       </c>
       <c r="B43" t="n">
-        <v>95202</v>
+        <v>90582</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5087,25 +5069,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5115,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514226</v>
+        <v>514287</v>
       </c>
       <c r="R43" t="n">
-        <v>6791259</v>
+        <v>6791297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,19 +5147,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119795232</v>
+        <v>119791871</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5212,7 +5194,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5222,14 +5204,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514150</v>
+        <v>514417</v>
       </c>
       <c r="R44" t="n">
-        <v>6791303</v>
+        <v>6790984</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5288,7 +5270,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119796166</v>
+        <v>119795232</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5323,7 +5305,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5337,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514100</v>
+        <v>514150</v>
       </c>
       <c r="R45" t="n">
-        <v>6791324</v>
+        <v>6791303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,10 +5381,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119790169</v>
+        <v>119794317</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>78782</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5411,47 +5393,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6459</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514594</v>
+        <v>514338</v>
       </c>
       <c r="R46" t="n">
-        <v>6790980</v>
+        <v>6791271</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,6 +5467,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5510,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119795133</v>
+        <v>119799502</v>
       </c>
       <c r="B47" t="n">
-        <v>90546</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5522,38 +5515,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514253</v>
+        <v>514168</v>
       </c>
       <c r="R47" t="n">
-        <v>6791221</v>
+        <v>6790929</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5596,26 +5598,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5632,10 +5614,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119800271</v>
+        <v>119790365</v>
       </c>
       <c r="B48" t="n">
-        <v>97811</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5644,38 +5626,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514404</v>
+        <v>514567</v>
       </c>
       <c r="R48" t="n">
-        <v>6790910</v>
+        <v>6790978</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5725,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119799531</v>
+        <v>119790576</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5746,38 +5737,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514129</v>
+        <v>514526</v>
       </c>
       <c r="R49" t="n">
-        <v>6790844</v>
+        <v>6790968</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119799989</v>
+        <v>119793661</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5848,25 +5848,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514153</v>
+        <v>514334</v>
       </c>
       <c r="R50" t="n">
-        <v>6790868</v>
+        <v>6791247</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119797154</v>
+        <v>119799989</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514045</v>
+        <v>514153</v>
       </c>
       <c r="R12" t="n">
-        <v>6791074</v>
+        <v>6790868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,22 +1830,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119799989</v>
+        <v>119797154</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514153</v>
+        <v>514045</v>
       </c>
       <c r="R13" t="n">
-        <v>6790868</v>
+        <v>6791074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,12 +1932,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119794869</v>
+        <v>119794575</v>
       </c>
       <c r="B15" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514269</v>
+        <v>514311</v>
       </c>
       <c r="R15" t="n">
-        <v>6791300</v>
+        <v>6791261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,22 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119794575</v>
+        <v>119798721</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,38 +2160,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514311</v>
+        <v>513988</v>
       </c>
       <c r="R16" t="n">
-        <v>6791261</v>
+        <v>6790833</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119798721</v>
+        <v>119800271</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,47 +2271,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513988</v>
+        <v>514404</v>
       </c>
       <c r="R17" t="n">
-        <v>6790833</v>
+        <v>6790910</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119800271</v>
+        <v>119794869</v>
       </c>
       <c r="B18" t="n">
-        <v>97811</v>
+        <v>95202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514404</v>
+        <v>514269</v>
       </c>
       <c r="R18" t="n">
-        <v>6790910</v>
+        <v>6791300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119796962</v>
+        <v>119799651</v>
       </c>
       <c r="B32" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,38 +3884,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514045</v>
+        <v>514163</v>
       </c>
       <c r="R32" t="n">
-        <v>6791074</v>
+        <v>6790947</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,19 +3971,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119799651</v>
+        <v>119799962</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4009,7 +4018,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4023,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514163</v>
+        <v>514169</v>
       </c>
       <c r="R33" t="n">
-        <v>6790947</v>
+        <v>6790900</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4085,7 +4094,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119799962</v>
+        <v>119799465</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4134,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514169</v>
+        <v>514129</v>
       </c>
       <c r="R34" t="n">
-        <v>6790900</v>
+        <v>6790844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4184,19 +4193,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119799465</v>
+        <v>119790198</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4231,7 +4240,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4245,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514129</v>
+        <v>514585</v>
       </c>
       <c r="R35" t="n">
-        <v>6790844</v>
+        <v>6790974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,22 +4304,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119790198</v>
+        <v>119796962</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,47 +4328,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514585</v>
+        <v>514045</v>
       </c>
       <c r="R36" t="n">
-        <v>6790974</v>
+        <v>6791074</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,12 +4406,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119799502</v>
+        <v>119793661</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5515,47 +5515,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514168</v>
+        <v>514334</v>
       </c>
       <c r="R47" t="n">
-        <v>6790929</v>
+        <v>6791247</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,7 +5605,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119790365</v>
+        <v>119799502</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5649,7 +5640,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5663,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514567</v>
+        <v>514168</v>
       </c>
       <c r="R48" t="n">
-        <v>6790978</v>
+        <v>6790929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,7 +5716,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119790576</v>
+        <v>119790365</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -5760,7 +5751,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5774,10 +5765,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514526</v>
+        <v>514567</v>
       </c>
       <c r="R49" t="n">
-        <v>6790968</v>
+        <v>6790978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,22 +5815,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119793661</v>
+        <v>119790576</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5848,38 +5839,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514334</v>
+        <v>514526</v>
       </c>
       <c r="R50" t="n">
-        <v>6791247</v>
+        <v>6790968</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119799989</v>
+        <v>119797154</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514153</v>
+        <v>514045</v>
       </c>
       <c r="R12" t="n">
-        <v>6790868</v>
+        <v>6791074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,22 +1830,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119797154</v>
+        <v>119799989</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514045</v>
+        <v>514153</v>
       </c>
       <c r="R13" t="n">
-        <v>6791074</v>
+        <v>6790868</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,12 +1932,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119794575</v>
+        <v>119794869</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514311</v>
+        <v>514269</v>
       </c>
       <c r="R15" t="n">
-        <v>6791261</v>
+        <v>6791300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,22 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119798721</v>
+        <v>119794575</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,47 +2160,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513988</v>
+        <v>514311</v>
       </c>
       <c r="R16" t="n">
-        <v>6790833</v>
+        <v>6791261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,22 +2238,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119800271</v>
+        <v>119798721</v>
       </c>
       <c r="B17" t="n">
-        <v>97811</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,38 +2262,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514404</v>
+        <v>513988</v>
       </c>
       <c r="R17" t="n">
-        <v>6790910</v>
+        <v>6790833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119794869</v>
+        <v>119800271</v>
       </c>
       <c r="B18" t="n">
-        <v>95202</v>
+        <v>97811</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514269</v>
+        <v>514404</v>
       </c>
       <c r="R18" t="n">
-        <v>6791300</v>
+        <v>6790910</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119799651</v>
+        <v>119796962</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,47 +3884,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514163</v>
+        <v>514045</v>
       </c>
       <c r="R32" t="n">
-        <v>6790947</v>
+        <v>6791074</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3971,19 +3962,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119799962</v>
+        <v>119799651</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4018,7 +4009,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4032,10 +4023,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514169</v>
+        <v>514163</v>
       </c>
       <c r="R33" t="n">
-        <v>6790900</v>
+        <v>6790947</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4094,7 +4085,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119799465</v>
+        <v>119799962</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4143,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514129</v>
+        <v>514169</v>
       </c>
       <c r="R34" t="n">
-        <v>6790844</v>
+        <v>6790900</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,19 +4184,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119790198</v>
+        <v>119799465</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4240,7 +4231,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514585</v>
+        <v>514129</v>
       </c>
       <c r="R35" t="n">
-        <v>6790974</v>
+        <v>6790844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4304,22 +4295,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119796962</v>
+        <v>119790198</v>
       </c>
       <c r="B36" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4328,38 +4319,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514045</v>
+        <v>514585</v>
       </c>
       <c r="R36" t="n">
-        <v>6791074</v>
+        <v>6790974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,12 +4406,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119793661</v>
+        <v>119799502</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5515,38 +5515,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514334</v>
+        <v>514168</v>
       </c>
       <c r="R47" t="n">
-        <v>6791247</v>
+        <v>6790929</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5605,7 +5614,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119799502</v>
+        <v>119790365</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5640,7 +5649,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5654,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514168</v>
+        <v>514567</v>
       </c>
       <c r="R48" t="n">
-        <v>6790929</v>
+        <v>6790978</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,7 +5725,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119790365</v>
+        <v>119790576</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -5751,7 +5760,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5765,10 +5774,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514567</v>
+        <v>514526</v>
       </c>
       <c r="R49" t="n">
-        <v>6790978</v>
+        <v>6790968</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5815,22 +5824,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119790576</v>
+        <v>119793661</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5839,47 +5848,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514526</v>
+        <v>514334</v>
       </c>
       <c r="R50" t="n">
-        <v>6790968</v>
+        <v>6791247</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119797154</v>
+        <v>119799989</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514045</v>
+        <v>514153</v>
       </c>
       <c r="R12" t="n">
-        <v>6791074</v>
+        <v>6790868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,22 +1830,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119799989</v>
+        <v>119797154</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514153</v>
+        <v>514045</v>
       </c>
       <c r="R13" t="n">
-        <v>6790868</v>
+        <v>6791074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,12 +1932,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119796962</v>
+        <v>119799651</v>
       </c>
       <c r="B32" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,38 +3884,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514045</v>
+        <v>514163</v>
       </c>
       <c r="R32" t="n">
-        <v>6791074</v>
+        <v>6790947</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,19 +3971,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119799651</v>
+        <v>119799962</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4009,7 +4018,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4023,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514163</v>
+        <v>514169</v>
       </c>
       <c r="R33" t="n">
-        <v>6790947</v>
+        <v>6790900</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4085,7 +4094,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119799962</v>
+        <v>119799465</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4134,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514169</v>
+        <v>514129</v>
       </c>
       <c r="R34" t="n">
-        <v>6790900</v>
+        <v>6790844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4184,19 +4193,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119799465</v>
+        <v>119790198</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4231,7 +4240,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4245,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514129</v>
+        <v>514585</v>
       </c>
       <c r="R35" t="n">
-        <v>6790844</v>
+        <v>6790974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,22 +4304,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119790198</v>
+        <v>119796962</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,47 +4328,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514585</v>
+        <v>514045</v>
       </c>
       <c r="R36" t="n">
-        <v>6790974</v>
+        <v>6791074</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,12 +4406,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119799502</v>
+        <v>119793661</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5515,47 +5515,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514168</v>
+        <v>514334</v>
       </c>
       <c r="R47" t="n">
-        <v>6790929</v>
+        <v>6791247</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,7 +5605,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119790365</v>
+        <v>119799502</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5649,7 +5640,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5663,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514567</v>
+        <v>514168</v>
       </c>
       <c r="R48" t="n">
-        <v>6790978</v>
+        <v>6790929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,7 +5716,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119790576</v>
+        <v>119790365</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -5760,7 +5751,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5774,10 +5765,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514526</v>
+        <v>514567</v>
       </c>
       <c r="R49" t="n">
-        <v>6790968</v>
+        <v>6790978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,22 +5815,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119793661</v>
+        <v>119790576</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5848,38 +5839,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514334</v>
+        <v>514526</v>
       </c>
       <c r="R50" t="n">
-        <v>6791247</v>
+        <v>6790968</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119795064</v>
+        <v>119795093</v>
       </c>
       <c r="B4" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514226</v>
+        <v>514237</v>
       </c>
       <c r="R4" t="n">
-        <v>6791259</v>
+        <v>6791250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119790568</v>
+        <v>119795064</v>
       </c>
       <c r="B5" t="n">
         <v>95202</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514543</v>
+        <v>514226</v>
       </c>
       <c r="R5" t="n">
-        <v>6790975</v>
+        <v>6791259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119795093</v>
+        <v>119790568</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514237</v>
+        <v>514543</v>
       </c>
       <c r="R6" t="n">
-        <v>6791250</v>
+        <v>6790975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119794869</v>
+        <v>119794575</v>
       </c>
       <c r="B15" t="n">
-        <v>95202</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514269</v>
+        <v>514311</v>
       </c>
       <c r="R15" t="n">
-        <v>6791300</v>
+        <v>6791261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,22 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119794575</v>
+        <v>119798721</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,38 +2160,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514311</v>
+        <v>513988</v>
       </c>
       <c r="R16" t="n">
-        <v>6791261</v>
+        <v>6790833</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119798721</v>
+        <v>119800271</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97811</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,47 +2271,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513988</v>
+        <v>514404</v>
       </c>
       <c r="R17" t="n">
-        <v>6790833</v>
+        <v>6790910</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119800271</v>
+        <v>119794869</v>
       </c>
       <c r="B18" t="n">
-        <v>97811</v>
+        <v>95202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514404</v>
+        <v>514269</v>
       </c>
       <c r="R18" t="n">
-        <v>6790910</v>
+        <v>6791300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119799651</v>
+        <v>119796962</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79511</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,47 +3884,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514163</v>
+        <v>514045</v>
       </c>
       <c r="R32" t="n">
-        <v>6790947</v>
+        <v>6791074</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3971,19 +3962,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119799962</v>
+        <v>119799651</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -4018,7 +4009,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4032,10 +4023,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514169</v>
+        <v>514163</v>
       </c>
       <c r="R33" t="n">
-        <v>6790900</v>
+        <v>6790947</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4094,7 +4085,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119799465</v>
+        <v>119799962</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4143,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514129</v>
+        <v>514169</v>
       </c>
       <c r="R34" t="n">
-        <v>6790844</v>
+        <v>6790900</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,19 +4184,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119790198</v>
+        <v>119799465</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4240,7 +4231,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514585</v>
+        <v>514129</v>
       </c>
       <c r="R35" t="n">
-        <v>6790974</v>
+        <v>6790844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4304,22 +4295,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119796962</v>
+        <v>119790198</v>
       </c>
       <c r="B36" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4328,38 +4319,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514045</v>
+        <v>514585</v>
       </c>
       <c r="R36" t="n">
-        <v>6791074</v>
+        <v>6790974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,12 +4406,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119793661</v>
+        <v>119799502</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5515,38 +5515,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514334</v>
+        <v>514168</v>
       </c>
       <c r="R47" t="n">
-        <v>6791247</v>
+        <v>6790929</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5605,7 +5614,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119799502</v>
+        <v>119790365</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5640,7 +5649,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5654,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514168</v>
+        <v>514567</v>
       </c>
       <c r="R48" t="n">
-        <v>6790929</v>
+        <v>6790978</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5716,7 +5725,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119790365</v>
+        <v>119790576</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -5751,7 +5760,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5765,10 +5774,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514567</v>
+        <v>514526</v>
       </c>
       <c r="R49" t="n">
-        <v>6790978</v>
+        <v>6790968</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5815,22 +5824,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119790576</v>
+        <v>119793661</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5839,47 +5848,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514526</v>
+        <v>514334</v>
       </c>
       <c r="R50" t="n">
-        <v>6790968</v>
+        <v>6791247</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119794575</v>
+        <v>119794869</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>95202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514311</v>
+        <v>514269</v>
       </c>
       <c r="R15" t="n">
-        <v>6791261</v>
+        <v>6791300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,22 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119798721</v>
+        <v>119794575</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,47 +2160,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513988</v>
+        <v>514311</v>
       </c>
       <c r="R16" t="n">
-        <v>6790833</v>
+        <v>6791261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,22 +2238,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119800271</v>
+        <v>119798721</v>
       </c>
       <c r="B17" t="n">
-        <v>97811</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,38 +2262,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514404</v>
+        <v>513988</v>
       </c>
       <c r="R17" t="n">
-        <v>6790910</v>
+        <v>6790833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119794869</v>
+        <v>119800271</v>
       </c>
       <c r="B18" t="n">
-        <v>95202</v>
+        <v>97811</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514269</v>
+        <v>514404</v>
       </c>
       <c r="R18" t="n">
-        <v>6791300</v>
+        <v>6790910</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119799413</v>
+        <v>119799962</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514145</v>
+        <v>514169</v>
       </c>
       <c r="R2" t="n">
-        <v>6790919</v>
+        <v>6790900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119791577</v>
+        <v>119797621</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514442</v>
+        <v>514045</v>
       </c>
       <c r="R3" t="n">
-        <v>6790946</v>
+        <v>6791074</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119795093</v>
+        <v>119800323</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514237</v>
+        <v>514384</v>
       </c>
       <c r="R4" t="n">
-        <v>6791250</v>
+        <v>6790930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119795064</v>
+        <v>119799787</v>
       </c>
       <c r="B5" t="n">
-        <v>95202</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,38 +1002,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514226</v>
+        <v>514108</v>
       </c>
       <c r="R5" t="n">
-        <v>6791259</v>
+        <v>6790973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119790568</v>
+        <v>119795093</v>
       </c>
       <c r="B6" t="n">
-        <v>95202</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514543</v>
+        <v>514237</v>
       </c>
       <c r="R6" t="n">
-        <v>6790975</v>
+        <v>6791250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119790391</v>
+        <v>119791871</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514546</v>
+        <v>514417</v>
       </c>
       <c r="R7" t="n">
-        <v>6790985</v>
+        <v>6790984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,22 +1302,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796795</v>
+        <v>119790365</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514065</v>
+        <v>514567</v>
       </c>
       <c r="R8" t="n">
-        <v>6791124</v>
+        <v>6790978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119795035</v>
+        <v>119795232</v>
       </c>
       <c r="B9" t="n">
-        <v>91861</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,38 +1437,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514287</v>
+        <v>514150</v>
       </c>
       <c r="R9" t="n">
-        <v>6791297</v>
+        <v>6791303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,22 +1524,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119799787</v>
+        <v>119796166</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1572,14 +1581,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514108</v>
+        <v>514100</v>
       </c>
       <c r="R10" t="n">
-        <v>6790973</v>
+        <v>6791324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,22 +1635,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119795197</v>
+        <v>119800022</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,38 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514150</v>
+        <v>514109</v>
       </c>
       <c r="R11" t="n">
-        <v>6791307</v>
+        <v>6790972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,22 +1737,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119799989</v>
+        <v>119799865</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1761,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514153</v>
+        <v>514173</v>
       </c>
       <c r="R12" t="n">
-        <v>6790868</v>
+        <v>6790969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119797154</v>
+        <v>119796795</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,38 +1872,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514045</v>
+        <v>514065</v>
       </c>
       <c r="R13" t="n">
-        <v>6791074</v>
+        <v>6791124</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,22 +1959,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119800029</v>
+        <v>119794575</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514147</v>
+        <v>514311</v>
       </c>
       <c r="R14" t="n">
-        <v>6790803</v>
+        <v>6791261</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,22 +2061,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119794869</v>
+        <v>119795089</v>
       </c>
       <c r="B15" t="n">
-        <v>95202</v>
+        <v>90600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514269</v>
+        <v>514287</v>
       </c>
       <c r="R15" t="n">
-        <v>6791300</v>
+        <v>6791297</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,22 +2163,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119794575</v>
+        <v>119799570</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,38 +2187,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514311</v>
+        <v>514165</v>
       </c>
       <c r="R16" t="n">
-        <v>6791261</v>
+        <v>6790935</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,22 +2274,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119798721</v>
+        <v>119794317</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>78798</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,47 +2298,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513988</v>
+        <v>514338</v>
       </c>
       <c r="R17" t="n">
-        <v>6790833</v>
+        <v>6791271</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,6 +2372,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2361,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119800271</v>
+        <v>119795197</v>
       </c>
       <c r="B18" t="n">
-        <v>97811</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,38 +2420,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514404</v>
+        <v>514150</v>
       </c>
       <c r="R18" t="n">
-        <v>6790910</v>
+        <v>6791307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119790169</v>
+        <v>119799906</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,7 +2545,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2512,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514594</v>
+        <v>514171</v>
       </c>
       <c r="R19" t="n">
-        <v>6790980</v>
+        <v>6790973</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796212</v>
+        <v>119795035</v>
       </c>
       <c r="B20" t="n">
-        <v>95455</v>
+        <v>91879</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2586,38 +2633,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514064</v>
+        <v>514287</v>
       </c>
       <c r="R20" t="n">
-        <v>6791315</v>
+        <v>6791297</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119795263</v>
+        <v>119791577</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,7 +2758,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2721,14 +2768,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514162</v>
+        <v>514442</v>
       </c>
       <c r="R21" t="n">
-        <v>6791322</v>
+        <v>6790946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119799930</v>
+        <v>119795064</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>95225</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,47 +2846,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514109</v>
+        <v>514226</v>
       </c>
       <c r="R22" t="n">
-        <v>6790972</v>
+        <v>6791259</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,22 +2924,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119800000</v>
+        <v>119799465</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,38 +2948,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514156</v>
+        <v>514129</v>
       </c>
       <c r="R23" t="n">
-        <v>6790891</v>
+        <v>6790844</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,22 +3035,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119799531</v>
+        <v>119799413</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,38 +3059,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514129</v>
+        <v>514145</v>
       </c>
       <c r="R24" t="n">
-        <v>6790844</v>
+        <v>6790919</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,22 +3146,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119799570</v>
+        <v>119800164</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3114,47 +3170,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514165</v>
+        <v>514290</v>
       </c>
       <c r="R25" t="n">
-        <v>6790935</v>
+        <v>6790882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119800022</v>
+        <v>119800271</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>97834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,25 +3272,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3300,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514109</v>
+        <v>514404</v>
       </c>
       <c r="R26" t="n">
-        <v>6790972</v>
+        <v>6790910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,22 +3350,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119800323</v>
+        <v>119799989</v>
       </c>
       <c r="B27" t="n">
-        <v>82305</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3327,25 +3374,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3355,10 +3402,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514384</v>
+        <v>514153</v>
       </c>
       <c r="R27" t="n">
-        <v>6790930</v>
+        <v>6790868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119795133</v>
+        <v>119799502</v>
       </c>
       <c r="B28" t="n">
-        <v>90546</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3429,38 +3476,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514253</v>
+        <v>514168</v>
       </c>
       <c r="R28" t="n">
-        <v>6791221</v>
+        <v>6790929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,26 +3559,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3539,10 +3575,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119799865</v>
+        <v>119790568</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>95225</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3551,47 +3587,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514173</v>
+        <v>514543</v>
       </c>
       <c r="R29" t="n">
-        <v>6790969</v>
+        <v>6790975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,10 +3677,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119796166</v>
+        <v>119799651</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,7 +3712,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3695,14 +3722,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514100</v>
+        <v>514163</v>
       </c>
       <c r="R30" t="n">
-        <v>6791324</v>
+        <v>6790947</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119799688</v>
+        <v>119799949</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3796,7 +3823,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3810,10 +3837,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514139</v>
+        <v>514186</v>
       </c>
       <c r="R31" t="n">
-        <v>6790955</v>
+        <v>6790923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,7 +3902,7 @@
         <v>119796962</v>
       </c>
       <c r="B32" t="n">
-        <v>79511</v>
+        <v>79527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3974,10 +4001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119799651</v>
+        <v>119796212</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>95478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3986,47 +4013,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514163</v>
+        <v>514064</v>
       </c>
       <c r="R33" t="n">
-        <v>6790947</v>
+        <v>6791315</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,22 +4091,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119799962</v>
+        <v>119790198</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4120,7 +4138,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4134,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514169</v>
+        <v>514585</v>
       </c>
       <c r="R34" t="n">
-        <v>6790900</v>
+        <v>6790974</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,10 +4214,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119799465</v>
+        <v>119793661</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4208,47 +4226,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514129</v>
+        <v>514334</v>
       </c>
       <c r="R35" t="n">
-        <v>6790844</v>
+        <v>6791247</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,22 +4304,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119790198</v>
+        <v>119800000</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,47 +4328,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514585</v>
+        <v>514156</v>
       </c>
       <c r="R36" t="n">
-        <v>6790974</v>
+        <v>6790891</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119799949</v>
+        <v>119794869</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>95225</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4430,47 +4430,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514186</v>
+        <v>514269</v>
       </c>
       <c r="R37" t="n">
-        <v>6790923</v>
+        <v>6791300</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4529,10 +4520,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119799906</v>
+        <v>119795263</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4564,7 +4555,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4574,14 +4565,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514171</v>
+        <v>514162</v>
       </c>
       <c r="R38" t="n">
-        <v>6790973</v>
+        <v>6791322</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,10 +4631,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119799434</v>
+        <v>119790391</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,38 +4643,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514151</v>
+        <v>514546</v>
       </c>
       <c r="R39" t="n">
-        <v>6790903</v>
+        <v>6790985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4730,22 +4730,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119800164</v>
+        <v>119795251</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,38 +4754,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514290</v>
+        <v>514156</v>
       </c>
       <c r="R40" t="n">
-        <v>6790882</v>
+        <v>6791319</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4844,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119795157</v>
+        <v>119795133</v>
       </c>
       <c r="B41" t="n">
-        <v>95202</v>
+        <v>90564</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4860,21 +4869,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2869</v>
+        <v>4660</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4884,10 +4893,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514196</v>
+        <v>514253</v>
       </c>
       <c r="R41" t="n">
-        <v>6791241</v>
+        <v>6791221</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4930,6 +4939,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4946,10 +4975,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119795251</v>
+        <v>119800029</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4958,47 +4987,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514156</v>
+        <v>514147</v>
       </c>
       <c r="R42" t="n">
-        <v>6791319</v>
+        <v>6790803</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119795089</v>
+        <v>119798721</v>
       </c>
       <c r="B43" t="n">
-        <v>90582</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5069,38 +5089,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514287</v>
+        <v>513988</v>
       </c>
       <c r="R43" t="n">
-        <v>6791297</v>
+        <v>6790833</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5147,22 +5176,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119791871</v>
+        <v>119790576</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5194,7 +5223,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5208,10 +5237,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514417</v>
+        <v>514526</v>
       </c>
       <c r="R44" t="n">
-        <v>6790984</v>
+        <v>6790968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5258,22 +5287,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119795232</v>
+        <v>119795157</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>95225</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5282,47 +5311,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514150</v>
+        <v>514196</v>
       </c>
       <c r="R45" t="n">
-        <v>6791303</v>
+        <v>6791241</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,10 +5401,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119794317</v>
+        <v>119799930</v>
       </c>
       <c r="B46" t="n">
-        <v>78782</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5393,38 +5413,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6459</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514338</v>
+        <v>514109</v>
       </c>
       <c r="R46" t="n">
-        <v>6791271</v>
+        <v>6790972</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5468,45 +5497,25 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119799502</v>
+        <v>119790169</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5538,7 +5547,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5552,10 +5561,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514168</v>
+        <v>514594</v>
       </c>
       <c r="R47" t="n">
-        <v>6790929</v>
+        <v>6790980</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,10 +5623,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119790365</v>
+        <v>119799688</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5649,7 +5658,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5663,10 +5672,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514567</v>
+        <v>514139</v>
       </c>
       <c r="R48" t="n">
-        <v>6790978</v>
+        <v>6790955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119790576</v>
+        <v>119799434</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5737,47 +5746,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514526</v>
+        <v>514151</v>
       </c>
       <c r="R49" t="n">
-        <v>6790968</v>
+        <v>6790903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,22 +5824,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119793661</v>
+        <v>119799531</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514334</v>
+        <v>514129</v>
       </c>
       <c r="R50" t="n">
-        <v>6791247</v>
+        <v>6790844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119799962</v>
+        <v>119790568</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514169</v>
+        <v>514543</v>
       </c>
       <c r="R2" t="n">
-        <v>6790900</v>
+        <v>6790975</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119797621</v>
+        <v>119794575</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514045</v>
+        <v>514311</v>
       </c>
       <c r="R3" t="n">
-        <v>6791074</v>
+        <v>6791261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119800323</v>
+        <v>119797154</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514384</v>
+        <v>514045</v>
       </c>
       <c r="R4" t="n">
-        <v>6790930</v>
+        <v>6791074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119799787</v>
+        <v>119790198</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514108</v>
+        <v>514585</v>
       </c>
       <c r="R5" t="n">
-        <v>6790973</v>
+        <v>6790974</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119795093</v>
+        <v>119795251</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,38 +1104,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514237</v>
+        <v>514156</v>
       </c>
       <c r="R6" t="n">
-        <v>6791250</v>
+        <v>6791319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119791871</v>
+        <v>119795232</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514417</v>
+        <v>514150</v>
       </c>
       <c r="R7" t="n">
-        <v>6790984</v>
+        <v>6791303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119790365</v>
+        <v>119799465</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514567</v>
+        <v>514129</v>
       </c>
       <c r="R8" t="n">
-        <v>6790978</v>
+        <v>6790844</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,19 +1413,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119795232</v>
+        <v>119799413</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1470,14 +1470,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514150</v>
+        <v>514145</v>
       </c>
       <c r="R9" t="n">
-        <v>6791303</v>
+        <v>6790919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796166</v>
+        <v>119795035</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>91879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,47 +1548,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514100</v>
+        <v>514287</v>
       </c>
       <c r="R10" t="n">
-        <v>6791324</v>
+        <v>6791297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119800022</v>
+        <v>119799865</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1650,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514109</v>
+        <v>514173</v>
       </c>
       <c r="R11" t="n">
-        <v>6790972</v>
+        <v>6790969</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,19 +1737,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119799865</v>
+        <v>119799988</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514173</v>
+        <v>514109</v>
       </c>
       <c r="R12" t="n">
-        <v>6790969</v>
+        <v>6790972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796795</v>
+        <v>119794317</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>78798</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,47 +1872,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6459</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514065</v>
+        <v>514338</v>
       </c>
       <c r="R13" t="n">
-        <v>6791124</v>
+        <v>6791271</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,6 +1946,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1971,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119794575</v>
+        <v>119796962</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1994,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514311</v>
+        <v>514045</v>
       </c>
       <c r="R14" t="n">
-        <v>6791261</v>
+        <v>6791074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119795089</v>
+        <v>119799787</v>
       </c>
       <c r="B15" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,38 +2096,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514287</v>
+        <v>514108</v>
       </c>
       <c r="R15" t="n">
-        <v>6791297</v>
+        <v>6790973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2195,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119799570</v>
+        <v>119799949</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2210,7 +2230,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514165</v>
+        <v>514186</v>
       </c>
       <c r="R16" t="n">
-        <v>6790935</v>
+        <v>6790923</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119794317</v>
+        <v>119800000</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,25 +2318,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2326,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514338</v>
+        <v>514156</v>
       </c>
       <c r="R17" t="n">
-        <v>6791271</v>
+        <v>6790891</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,26 +2392,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119795197</v>
+        <v>119799989</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,38 +2420,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514150</v>
+        <v>514153</v>
       </c>
       <c r="R18" t="n">
-        <v>6791307</v>
+        <v>6790868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799906</v>
+        <v>119795263</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514171</v>
+        <v>514162</v>
       </c>
       <c r="R19" t="n">
-        <v>6790973</v>
+        <v>6791322</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119795035</v>
+        <v>119800271</v>
       </c>
       <c r="B20" t="n">
-        <v>91879</v>
+        <v>97834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,21 +2637,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514287</v>
+        <v>514404</v>
       </c>
       <c r="R20" t="n">
-        <v>6791297</v>
+        <v>6790910</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,19 +2711,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119791577</v>
+        <v>119799688</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514442</v>
+        <v>514139</v>
       </c>
       <c r="R21" t="n">
-        <v>6790946</v>
+        <v>6790955</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119795064</v>
+        <v>119795089</v>
       </c>
       <c r="B22" t="n">
-        <v>95225</v>
+        <v>90600</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,25 +2846,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514226</v>
+        <v>514287</v>
       </c>
       <c r="R22" t="n">
-        <v>6791259</v>
+        <v>6791297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,22 +2924,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119799465</v>
+        <v>119799531</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,37 +2948,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
@@ -3047,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119799413</v>
+        <v>119793661</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,47 +3050,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514145</v>
+        <v>514334</v>
       </c>
       <c r="R24" t="n">
-        <v>6790919</v>
+        <v>6791247</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3158,10 +3140,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119800164</v>
+        <v>119791871</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3170,38 +3152,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514290</v>
+        <v>514417</v>
       </c>
       <c r="R25" t="n">
-        <v>6790882</v>
+        <v>6790984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119800271</v>
+        <v>119800164</v>
       </c>
       <c r="B26" t="n">
-        <v>97834</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3272,25 +3263,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3300,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514404</v>
+        <v>514290</v>
       </c>
       <c r="R26" t="n">
-        <v>6790910</v>
+        <v>6790882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119799989</v>
+        <v>119790391</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3374,38 +3365,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514153</v>
+        <v>514546</v>
       </c>
       <c r="R27" t="n">
-        <v>6790868</v>
+        <v>6790985</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,22 +3452,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119799502</v>
+        <v>119795157</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3476,47 +3476,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514168</v>
+        <v>514196</v>
       </c>
       <c r="R28" t="n">
-        <v>6790929</v>
+        <v>6791241</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,10 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119790568</v>
+        <v>119799502</v>
       </c>
       <c r="B29" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3587,38 +3578,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514543</v>
+        <v>514168</v>
       </c>
       <c r="R29" t="n">
-        <v>6790975</v>
+        <v>6790929</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119799651</v>
+        <v>119795093</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3689,47 +3689,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514163</v>
+        <v>514237</v>
       </c>
       <c r="R30" t="n">
-        <v>6790947</v>
+        <v>6791250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,7 +3779,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119799949</v>
+        <v>119795197</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3821,26 +3812,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514186</v>
+        <v>514150</v>
       </c>
       <c r="R31" t="n">
-        <v>6790923</v>
+        <v>6791307</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,10 +3881,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119796962</v>
+        <v>119799570</v>
       </c>
       <c r="B32" t="n">
-        <v>79527</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3911,38 +3893,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514045</v>
+        <v>514165</v>
       </c>
       <c r="R32" t="n">
-        <v>6791074</v>
+        <v>6790935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3989,22 +3980,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119796212</v>
+        <v>119800029</v>
       </c>
       <c r="B33" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,34 +4008,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514064</v>
+        <v>514147</v>
       </c>
       <c r="R33" t="n">
-        <v>6791315</v>
+        <v>6790803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4091,19 +4082,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119790198</v>
+        <v>119796166</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4138,7 +4129,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4148,14 +4139,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514585</v>
+        <v>514100</v>
       </c>
       <c r="R34" t="n">
-        <v>6790974</v>
+        <v>6791324</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4214,10 +4205,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119793661</v>
+        <v>119795133</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90564</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4226,25 +4217,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514334</v>
+        <v>514253</v>
       </c>
       <c r="R35" t="n">
-        <v>6791247</v>
+        <v>6791221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4300,6 +4291,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4316,10 +4327,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119800000</v>
+        <v>119799651</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4328,38 +4339,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514156</v>
+        <v>514163</v>
       </c>
       <c r="R36" t="n">
-        <v>6790891</v>
+        <v>6790947</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,10 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119794869</v>
+        <v>119790169</v>
       </c>
       <c r="B37" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4430,38 +4450,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514269</v>
+        <v>514594</v>
       </c>
       <c r="R37" t="n">
-        <v>6791300</v>
+        <v>6790980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4520,7 +4549,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119795263</v>
+        <v>119799906</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4555,7 +4584,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4565,14 +4594,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514162</v>
+        <v>514171</v>
       </c>
       <c r="R38" t="n">
-        <v>6791322</v>
+        <v>6790973</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,7 +4660,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119790391</v>
+        <v>119799962</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4666,7 +4695,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4680,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514546</v>
+        <v>514169</v>
       </c>
       <c r="R39" t="n">
-        <v>6790985</v>
+        <v>6790900</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4730,22 +4759,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119795251</v>
+        <v>119796212</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,47 +4783,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514156</v>
+        <v>514064</v>
       </c>
       <c r="R40" t="n">
-        <v>6791319</v>
+        <v>6791315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4841,22 +4861,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119795133</v>
+        <v>119800022</v>
       </c>
       <c r="B41" t="n">
-        <v>90564</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4865,25 +4885,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4893,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514253</v>
+        <v>514109</v>
       </c>
       <c r="R41" t="n">
-        <v>6791221</v>
+        <v>6790972</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4940,45 +4960,25 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119800029</v>
+        <v>119799434</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514147</v>
+        <v>514151</v>
       </c>
       <c r="R42" t="n">
-        <v>6790803</v>
+        <v>6790903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119798721</v>
+        <v>119790365</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513988</v>
+        <v>514567</v>
       </c>
       <c r="R43" t="n">
-        <v>6790833</v>
+        <v>6790978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119790576</v>
+        <v>119798721</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514526</v>
+        <v>513988</v>
       </c>
       <c r="R44" t="n">
-        <v>6790968</v>
+        <v>6790833</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5287,22 +5287,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119795157</v>
+        <v>119790576</v>
       </c>
       <c r="B45" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5311,38 +5311,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514196</v>
+        <v>514526</v>
       </c>
       <c r="R45" t="n">
-        <v>6791241</v>
+        <v>6790968</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5389,22 +5398,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119799930</v>
+        <v>119794869</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5413,47 +5422,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514109</v>
+        <v>514269</v>
       </c>
       <c r="R46" t="n">
-        <v>6790972</v>
+        <v>6791300</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5500,19 +5500,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119790169</v>
+        <v>119796795</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514594</v>
+        <v>514065</v>
       </c>
       <c r="R47" t="n">
-        <v>6790980</v>
+        <v>6791124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119799688</v>
+        <v>119791577</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514139</v>
+        <v>514442</v>
       </c>
       <c r="R48" t="n">
-        <v>6790955</v>
+        <v>6790946</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119799434</v>
+        <v>119800323</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514151</v>
+        <v>514384</v>
       </c>
       <c r="R49" t="n">
-        <v>6790903</v>
+        <v>6790930</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119799531</v>
+        <v>119795064</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5848,25 +5848,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514129</v>
+        <v>514226</v>
       </c>
       <c r="R50" t="n">
-        <v>6790844</v>
+        <v>6791259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5926,12 +5926,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22054-2020 artfynd.xlsx
+++ b/artfynd/A 22054-2020 artfynd.xlsx
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119795035</v>
+        <v>119799865</v>
       </c>
       <c r="B10" t="n">
-        <v>91879</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,38 +1548,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514287</v>
+        <v>514173</v>
       </c>
       <c r="R10" t="n">
-        <v>6791297</v>
+        <v>6790969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,22 +1635,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119799865</v>
+        <v>119795035</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>91879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,47 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514173</v>
+        <v>514287</v>
       </c>
       <c r="R11" t="n">
-        <v>6790969</v>
+        <v>6791297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,12 +1737,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119795093</v>
+        <v>119800029</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514237</v>
+        <v>514147</v>
       </c>
       <c r="R30" t="n">
-        <v>6791250</v>
+        <v>6790803</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119795197</v>
+        <v>119795093</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,38 +3791,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
+          <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514150</v>
+        <v>514237</v>
       </c>
       <c r="R31" t="n">
-        <v>6791307</v>
+        <v>6791250</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119799570</v>
+        <v>119795197</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3914,26 +3914,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jässelåsen, Jässelåsen, Dlr</t>
+          <t>Björnbergsslogarna, Björnbergsslogarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514165</v>
+        <v>514150</v>
       </c>
       <c r="R32" t="n">
-        <v>6790935</v>
+        <v>6791307</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3992,10 +3983,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119800029</v>
+        <v>119799570</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4004,38 +3995,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jässelåsen, Jässelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514147</v>
+        <v>514165</v>
       </c>
       <c r="R33" t="n">
-        <v>6790803</v>
+        <v>6790935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
